--- a/Donnees/Statistiques Démographiques et sociales/Emploi/Portail_Tableau_Emploi_2012-2019.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Emploi/Portail_Tableau_Emploi_2012-2019.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Emploi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE168D59-33D5-4FB8-B281-D0FFA95210D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397DE03A-6E42-46E9-B49F-284546F9CC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="901" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Taux de participation" sheetId="7" r:id="rId1"/>
@@ -35,15 +35,6 @@
     <t>National</t>
   </si>
   <si>
-    <t>Tableau 1: Taux de participation</t>
-  </si>
-  <si>
-    <t>Tableau 2: Ratio emploi (Proportion des personnes en emploi sur la population en âge de travailler)</t>
-  </si>
-  <si>
-    <t>Tableau 3: Taux de chômage</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Wilaya~Assaba</t>
   </si>
   <si>
@@ -122,12 +113,6 @@
     <t xml:space="preserve"> Wilaya~Tiris Zemmour</t>
   </si>
   <si>
-    <t>Source: 
-2012: Enquête Nationale de Référence sur l'Emploi et le Secteur Informel (ENRE-SI)
-2017: Enquête Nationale sur l'Emploi et le Secteur Informel (ENE-SI)
-2014 et 2019: Enquête Permanente sur les Conditions de Vie des ménages (EPCV)</t>
-  </si>
-  <si>
     <t>groupe age~Total</t>
   </si>
   <si>
@@ -138,6 +123,18 @@
   </si>
   <si>
     <t>groupe age~36 - 64</t>
+  </si>
+  <si>
+    <t>Tableau 1.5.1: Taux de participation au marché de travail</t>
+  </si>
+  <si>
+    <t>Source : ENRE-SI/2012, ENE-SI/2017 et EPCV/2019</t>
+  </si>
+  <si>
+    <t>Tableau 1.5.2: Ratio emploi (Proportion des personnes en emploi sur la population en âge de travailler)</t>
+  </si>
+  <si>
+    <t>Tableau 1.5.3: Taux de chômage (population en chômage)</t>
   </si>
 </sst>
 </file>
@@ -642,7 +639,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -685,7 +682,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B4" s="5">
         <v>45.848093455717887</v>
@@ -703,7 +700,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5">
         <v>49.51442249627187</v>
@@ -721,7 +718,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5">
         <v>42.2951965109553</v>
@@ -739,7 +736,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5">
         <v>46.749115163429046</v>
@@ -757,7 +754,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="5">
         <v>38.504688499977128</v>
@@ -775,7 +772,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="5">
         <v>24.084872522914374</v>
@@ -793,7 +790,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="5">
         <v>36.861997713228796</v>
@@ -811,7 +808,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="5">
         <v>48.796407760070387</v>
@@ -829,7 +826,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5">
         <v>48.747550999929224</v>
@@ -847,7 +844,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" s="5">
         <v>51.145278209192554</v>
@@ -865,7 +862,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5">
         <v>38.717380848562222</v>
@@ -883,7 +880,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" s="5">
         <v>45.986086034915189</v>
@@ -901,7 +898,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5">
         <v>45.016191966537292</v>
@@ -919,7 +916,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5">
         <v>43.548886268371497</v>
@@ -937,7 +934,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B18" s="5">
         <v>43.89018289864164</v>
@@ -955,7 +952,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="5">
         <v>43.25427126014737</v>
@@ -973,7 +970,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B20" s="5">
         <v>43.548886268371497</v>
@@ -991,7 +988,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B21" s="5">
         <v>62.792768064363685</v>
@@ -1009,7 +1006,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B22" s="5">
         <v>28.316649161824678</v>
@@ -1027,7 +1024,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B23" s="5">
         <v>43.548886268371497</v>
@@ -1045,7 +1042,7 @@
     </row>
     <row r="24" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B24" s="5">
         <v>46.266006972320113</v>
@@ -1063,7 +1060,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B25" s="5">
         <v>42.605201660015716</v>
@@ -1081,7 +1078,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B26" s="5">
         <v>33.072547998476153</v>
@@ -1099,7 +1096,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B27" s="5">
         <v>61.225672608273918</v>
@@ -1117,7 +1114,7 @@
     </row>
     <row r="28" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B28" s="5">
         <v>46.269855628125683</v>
@@ -1135,7 +1132,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B29" s="5">
         <v>49.182313444584317</v>
@@ -1153,7 +1150,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5">
         <v>43.548886268371497</v>
@@ -1171,7 +1168,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B31" s="5">
         <v>23.306558727872897</v>
@@ -1189,7 +1186,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5">
         <v>52.191853516548747</v>
@@ -1207,7 +1204,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5">
         <v>57.358499002863574</v>
@@ -1223,9 +1220,9 @@
       </c>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6" ht="138" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="3"/>
@@ -1283,7 +1280,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1329,7 +1326,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B4" s="5">
         <v>44.193148895573032</v>
@@ -1347,7 +1344,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5">
         <v>47.399400156228559</v>
@@ -1365,7 +1362,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5">
         <v>39.922050742838536</v>
@@ -1383,7 +1380,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5">
         <v>45.467707625714922</v>
@@ -1401,7 +1398,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="5">
         <v>34.278493346731295</v>
@@ -1419,7 +1416,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="5">
         <v>22.768220276887451</v>
@@ -1437,7 +1434,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="5">
         <v>31.842812106271637</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="5">
         <v>37.748216878350448</v>
@@ -1473,7 +1470,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5">
         <v>39.415899720930852</v>
@@ -1491,7 +1488,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" s="5">
         <v>50.342135104640839</v>
@@ -1509,7 +1506,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5">
         <v>34.225329626270423</v>
@@ -1527,7 +1524,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" s="5">
         <v>32.74972399372156</v>
@@ -1545,7 +1542,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5">
         <v>37.499742294623481</v>
@@ -1563,7 +1560,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5">
         <v>39.161907611268383</v>
@@ -1581,7 +1578,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B18" s="5">
         <v>36.615324857087458</v>
@@ -1599,7 +1596,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="5">
         <v>41.360175723298553</v>
@@ -1617,7 +1614,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B20" s="5">
         <v>39.161907611268383</v>
@@ -1635,7 +1632,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B21" s="5">
         <v>57.386390936436719</v>
@@ -1653,7 +1650,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B22" s="5">
         <v>24.736561722317333</v>
@@ -1671,7 +1668,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B23" s="5">
         <v>39.161907611268383</v>
@@ -1689,7 +1686,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B24" s="5">
         <v>43.631372960961286</v>
@@ -1707,7 +1704,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B25" s="5">
         <v>36.402033546757878</v>
@@ -1725,7 +1722,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B26" s="5">
         <v>27.518088048485573</v>
@@ -1743,7 +1740,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B27" s="5">
         <v>53.610908286812865</v>
@@ -1761,7 +1758,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B28" s="5">
         <v>38.12686902539857</v>
@@ -1779,7 +1776,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B29" s="5">
         <v>46.708485917700983</v>
@@ -1797,7 +1794,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5">
         <v>39.161907611268383</v>
@@ -1815,7 +1812,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B31" s="5">
         <v>19.842309880872527</v>
@@ -1833,7 +1830,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5">
         <v>45.044123768540274</v>
@@ -1851,7 +1848,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5">
         <v>54.154547160777213</v>
@@ -1867,9 +1864,9 @@
       </c>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="3"/>
@@ -1927,7 +1924,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1970,7 +1967,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B4" s="5">
         <v>3.6096256908550886</v>
@@ -1987,7 +1984,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5">
         <v>4.2715278365662313</v>
@@ -2004,7 +2001,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5">
         <v>5.6109108454010981</v>
@@ -2021,7 +2018,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5">
         <v>2.7410305697434683</v>
@@ -2038,7 +2035,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="5">
         <v>10.97579364458009</v>
@@ -2055,7 +2052,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="5">
         <v>5.4667187662059069</v>
@@ -2072,7 +2069,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="5">
         <v>13.616151913426698</v>
@@ -2089,7 +2086,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="5">
         <v>22.641402080340232</v>
@@ -2106,7 +2103,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5">
         <v>19.142810433721756</v>
@@ -2123,7 +2120,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" s="5">
         <v>1.5703172075176992</v>
@@ -2140,7 +2137,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5">
         <v>11.602156767426591</v>
@@ -2157,7 +2154,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" s="5">
         <v>28.783406422420423</v>
@@ -2174,7 +2171,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5">
         <v>16.697213477099638</v>
@@ -2191,7 +2188,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5">
         <v>10.073687373009472</v>
@@ -2208,7 +2205,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B18" s="5">
         <v>16.575137219989511</v>
@@ -2225,7 +2222,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="5">
         <v>4.3789791890310541</v>
@@ -2242,7 +2239,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B20" s="5">
         <v>10.073687373009472</v>
@@ -2259,7 +2256,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B21" s="5">
         <v>8.6098722744397307</v>
@@ -2276,7 +2273,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B22" s="5">
         <v>12.643047625613544</v>
@@ -2293,7 +2290,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B23" s="5">
         <v>10.073687373009472</v>
@@ -2310,7 +2307,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B24" s="5">
         <v>5.694535110702776</v>
@@ -2327,7 +2324,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B25" s="5">
         <v>14.559649694322388</v>
@@ -2344,7 +2341,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B26" s="5">
         <v>16.794774778908845</v>
@@ -2361,7 +2358,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B27" s="5">
         <v>12.437208113957086</v>
@@ -2378,7 +2375,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B28" s="5">
         <v>17.598902119282393</v>
@@ -2395,7 +2392,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B29" s="5">
         <v>5.0299128967790256</v>
@@ -2412,7 +2409,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5">
         <v>10.073687373009472</v>
@@ -2429,7 +2426,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B31" s="5">
         <v>14.863836774227304</v>
@@ -2446,7 +2443,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5">
         <v>13.695106163918972</v>
@@ -2463,7 +2460,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5">
         <v>5.5858362714940899</v>
@@ -2478,9 +2475,9 @@
         <v>5.175094288070353</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
